--- a/data/sars/pacific/tables/Pacific_2011_Appendix3.xlsx
+++ b/data/sars/pacific/tables/Pacific_2011_Appendix3.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cfree/Dropbox/Chris/UCSB/projects/marine_mammals/us_sar_synthesis/data/sars/pacific/tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54ED5940-11BE-3F47-8C42-347912334C58}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A16A001C-0ABD-5F45-8FA4-3DE2BB0144F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="120" yWindow="500" windowWidth="30340" windowHeight="17960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="473" uniqueCount="123">
   <si>
     <t>California sea lion</t>
   </si>
@@ -340,9 +340,6 @@
     <t>survey3</t>
   </si>
   <si>
-    <t>revised</t>
-  </si>
-  <si>
     <t>species</t>
   </si>
   <si>
@@ -377,6 +374,21 @@
   </si>
   <si>
     <t>rf</t>
+  </si>
+  <si>
+    <t>notes</t>
+  </si>
+  <si>
+    <t>RF=0.5 in SAR; RF=0.4 was typo in table</t>
+  </si>
+  <si>
+    <t>revised_yn</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <t>revision_yr</t>
   </si>
 </sst>
 </file>
@@ -793,7 +805,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q78"/>
+  <dimension ref="A1:R78"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="42.59765625" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="32.59765625" style="1" bestFit="1" customWidth="1"/>
@@ -808,47 +820,48 @@
     <col min="11" max="11" width="14.19921875" style="1" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="13.3984375" style="1" bestFit="1" customWidth="1"/>
     <col min="13" max="15" width="9.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.59765625" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="18.3984375" style="1" customWidth="1"/>
-    <col min="18" max="16384" width="42.59765625" style="1"/>
+    <col min="16" max="16" width="13.59765625" style="1" customWidth="1"/>
+    <col min="17" max="17" width="14" style="1" customWidth="1"/>
+    <col min="18" max="18" width="50.3984375" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="42.59765625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A1" s="5" t="s">
+        <v>106</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="C1" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="D1" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="E1" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="F1" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="F1" s="5" t="s">
+      <c r="G1" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="G1" s="5" t="s">
+      <c r="H1" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="I1" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="H1" s="5" t="s">
-        <v>118</v>
-      </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>116</v>
-      </c>
-      <c r="L1" s="5" t="s">
-        <v>117</v>
       </c>
       <c r="M1" s="5" t="s">
         <v>103</v>
@@ -860,11 +873,16 @@
         <v>105</v>
       </c>
       <c r="P1" s="5" t="s">
-        <v>106</v>
-      </c>
-      <c r="Q1" s="3"/>
-    </row>
-    <row r="2" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+        <v>122</v>
+      </c>
+      <c r="Q1" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="R1" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
@@ -913,8 +931,11 @@
       <c r="P2" s="9">
         <v>2011</v>
       </c>
-    </row>
-    <row r="3" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q2" s="9" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A3" s="6" t="s">
         <v>7</v>
       </c>
@@ -963,8 +984,11 @@
       <c r="P3" s="9">
         <v>2011</v>
       </c>
-    </row>
-    <row r="4" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q3" s="9" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A4" s="5" t="s">
         <v>7</v>
       </c>
@@ -1009,8 +1033,9 @@
       <c r="P4" s="11">
         <v>2010</v>
       </c>
-    </row>
-    <row r="5" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q4" s="11"/>
+    </row>
+    <row r="5" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A5" s="5" t="s">
         <v>7</v>
       </c>
@@ -1055,8 +1080,9 @@
       <c r="P5" s="11">
         <v>2010</v>
       </c>
-    </row>
-    <row r="6" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q5" s="11"/>
+    </row>
+    <row r="6" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A6" s="5" t="s">
         <v>16</v>
       </c>
@@ -1105,8 +1131,9 @@
       <c r="P6" s="11">
         <v>2007</v>
       </c>
-    </row>
-    <row r="7" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q6" s="11"/>
+    </row>
+    <row r="7" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A7" s="5" t="s">
         <v>20</v>
       </c>
@@ -1151,8 +1178,9 @@
       <c r="P7" s="11">
         <v>2000</v>
       </c>
-    </row>
-    <row r="8" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q7" s="11"/>
+    </row>
+    <row r="8" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A8" s="5" t="s">
         <v>23</v>
       </c>
@@ -1201,8 +1229,9 @@
       <c r="P8" s="11">
         <v>2010</v>
       </c>
-    </row>
-    <row r="9" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q8" s="11"/>
+    </row>
+    <row r="9" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A9" s="6" t="s">
         <v>25</v>
       </c>
@@ -1251,8 +1280,11 @@
       <c r="P9" s="9">
         <v>2011</v>
       </c>
-    </row>
-    <row r="10" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q9" s="9" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A10" s="5" t="s">
         <v>30</v>
       </c>
@@ -1301,8 +1333,9 @@
       <c r="P10" s="11">
         <v>2009</v>
       </c>
-    </row>
-    <row r="11" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q10" s="11"/>
+    </row>
+    <row r="11" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A11" s="5" t="s">
         <v>30</v>
       </c>
@@ -1351,8 +1384,9 @@
       <c r="P11" s="11">
         <v>2009</v>
       </c>
-    </row>
-    <row r="12" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q11" s="11"/>
+    </row>
+    <row r="12" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A12" s="5" t="s">
         <v>30</v>
       </c>
@@ -1401,8 +1435,9 @@
       <c r="P12" s="11">
         <v>2009</v>
       </c>
-    </row>
-    <row r="13" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q12" s="11"/>
+    </row>
+    <row r="13" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A13" s="5" t="s">
         <v>30</v>
       </c>
@@ -1451,8 +1486,9 @@
       <c r="P13" s="11">
         <v>2009</v>
       </c>
-    </row>
-    <row r="14" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q13" s="11"/>
+    </row>
+    <row r="14" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A14" s="6" t="s">
         <v>30</v>
       </c>
@@ -1501,8 +1537,11 @@
       <c r="P14" s="9">
         <v>2011</v>
       </c>
-    </row>
-    <row r="15" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q14" s="9" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A15" s="6" t="s">
         <v>30</v>
       </c>
@@ -1551,8 +1590,11 @@
       <c r="P15" s="9">
         <v>2011</v>
       </c>
-    </row>
-    <row r="16" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q15" s="9" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A16" s="5" t="s">
         <v>41</v>
       </c>
@@ -1601,8 +1643,9 @@
       <c r="P16" s="11">
         <v>2010</v>
       </c>
-    </row>
-    <row r="17" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q16" s="11"/>
+    </row>
+    <row r="17" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A17" s="5" t="s">
         <v>44</v>
       </c>
@@ -1651,8 +1694,9 @@
       <c r="P17" s="11">
         <v>2010</v>
       </c>
-    </row>
-    <row r="18" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q17" s="11"/>
+    </row>
+    <row r="18" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A18" s="5" t="s">
         <v>45</v>
       </c>
@@ -1701,8 +1745,9 @@
       <c r="P18" s="11">
         <v>2010</v>
       </c>
-    </row>
-    <row r="19" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q18" s="11"/>
+    </row>
+    <row r="19" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A19" s="5" t="s">
         <v>46</v>
       </c>
@@ -1751,8 +1796,9 @@
       <c r="P19" s="11">
         <v>2008</v>
       </c>
-    </row>
-    <row r="20" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q19" s="11"/>
+    </row>
+    <row r="20" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A20" s="5" t="s">
         <v>46</v>
       </c>
@@ -1801,8 +1847,9 @@
       <c r="P20" s="11">
         <v>2010</v>
       </c>
-    </row>
-    <row r="21" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q20" s="11"/>
+    </row>
+    <row r="21" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A21" s="5" t="s">
         <v>50</v>
       </c>
@@ -1851,8 +1898,9 @@
       <c r="P21" s="11">
         <v>2010</v>
       </c>
-    </row>
-    <row r="22" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q21" s="11"/>
+    </row>
+    <row r="22" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A22" s="5" t="s">
         <v>51</v>
       </c>
@@ -1901,8 +1949,9 @@
       <c r="P22" s="11">
         <v>2010</v>
       </c>
-    </row>
-    <row r="23" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q22" s="11"/>
+    </row>
+    <row r="23" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A23" s="5" t="s">
         <v>52</v>
       </c>
@@ -1951,8 +2000,9 @@
       <c r="P23" s="11">
         <v>2010</v>
       </c>
-    </row>
-    <row r="24" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q23" s="11"/>
+    </row>
+    <row r="24" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A24" s="5" t="s">
         <v>53</v>
       </c>
@@ -2001,8 +2051,9 @@
       <c r="P24" s="11">
         <v>2010</v>
       </c>
-    </row>
-    <row r="25" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q24" s="11"/>
+    </row>
+    <row r="25" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A25" s="5" t="s">
         <v>54</v>
       </c>
@@ -2051,8 +2102,9 @@
       <c r="P25" s="11">
         <v>2010</v>
       </c>
-    </row>
-    <row r="26" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q25" s="11"/>
+    </row>
+    <row r="26" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A26" s="6" t="s">
         <v>54</v>
       </c>
@@ -2101,8 +2153,11 @@
       <c r="P26" s="9">
         <v>2011</v>
       </c>
-    </row>
-    <row r="27" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q26" s="9" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="27" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A27" s="5" t="s">
         <v>58</v>
       </c>
@@ -2125,7 +2180,7 @@
         <v>0.04</v>
       </c>
       <c r="H27" s="14">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="I27" s="14">
         <v>4.5999999999999996</v>
@@ -2151,8 +2206,12 @@
       <c r="P27" s="11">
         <v>2010</v>
       </c>
-    </row>
-    <row r="28" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q27" s="11"/>
+      <c r="R27" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="28" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A28" s="5" t="s">
         <v>59</v>
       </c>
@@ -2201,8 +2260,9 @@
       <c r="P28" s="11">
         <v>2010</v>
       </c>
-    </row>
-    <row r="29" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q28" s="11"/>
+    </row>
+    <row r="29" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A29" s="5" t="s">
         <v>60</v>
       </c>
@@ -2251,8 +2311,9 @@
       <c r="P29" s="11">
         <v>2010</v>
       </c>
-    </row>
-    <row r="30" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q29" s="11"/>
+    </row>
+    <row r="30" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A30" s="5" t="s">
         <v>61</v>
       </c>
@@ -2301,8 +2362,9 @@
       <c r="P30" s="11">
         <v>2010</v>
       </c>
-    </row>
-    <row r="31" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q30" s="11"/>
+    </row>
+    <row r="31" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A31" s="5" t="s">
         <v>62</v>
       </c>
@@ -2351,8 +2413,9 @@
       <c r="P31" s="11">
         <v>2010</v>
       </c>
-    </row>
-    <row r="32" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q31" s="11"/>
+    </row>
+    <row r="32" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A32" s="5" t="s">
         <v>63</v>
       </c>
@@ -2401,8 +2464,9 @@
       <c r="P32" s="11">
         <v>2010</v>
       </c>
-    </row>
-    <row r="33" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q32" s="11"/>
+    </row>
+    <row r="33" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A33" s="5" t="s">
         <v>64</v>
       </c>
@@ -2451,8 +2515,9 @@
       <c r="P33" s="11">
         <v>2010</v>
       </c>
-    </row>
-    <row r="34" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q33" s="11"/>
+    </row>
+    <row r="34" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A34" s="5" t="s">
         <v>65</v>
       </c>
@@ -2501,8 +2566,9 @@
       <c r="P34" s="11">
         <v>2010</v>
       </c>
-    </row>
-    <row r="35" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q34" s="11"/>
+    </row>
+    <row r="35" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A35" s="5" t="s">
         <v>68</v>
       </c>
@@ -2551,8 +2617,9 @@
       <c r="P35" s="11">
         <v>2010</v>
       </c>
-    </row>
-    <row r="36" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q35" s="11"/>
+    </row>
+    <row r="36" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A36" s="5" t="s">
         <v>70</v>
       </c>
@@ -2601,8 +2668,9 @@
       <c r="P36" s="11">
         <v>2010</v>
       </c>
-    </row>
-    <row r="37" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q36" s="11"/>
+    </row>
+    <row r="37" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A37" s="5" t="s">
         <v>71</v>
       </c>
@@ -2651,8 +2719,9 @@
       <c r="P37" s="11">
         <v>2010</v>
       </c>
-    </row>
-    <row r="38" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q37" s="11"/>
+    </row>
+    <row r="38" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A38" s="5" t="s">
         <v>72</v>
       </c>
@@ -2701,8 +2770,9 @@
       <c r="P38" s="11">
         <v>2010</v>
       </c>
-    </row>
-    <row r="39" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q38" s="11"/>
+    </row>
+    <row r="39" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A39" s="5" t="s">
         <v>73</v>
       </c>
@@ -2747,8 +2817,9 @@
       <c r="P39" s="11">
         <v>2010</v>
       </c>
-    </row>
-    <row r="40" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q39" s="11"/>
+    </row>
+    <row r="40" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A40" s="5" t="s">
         <v>73</v>
       </c>
@@ -2797,8 +2868,9 @@
       <c r="P40" s="11">
         <v>2010</v>
       </c>
-    </row>
-    <row r="41" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q40" s="11"/>
+    </row>
+    <row r="41" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A41" s="5" t="s">
         <v>45</v>
       </c>
@@ -2843,9 +2915,10 @@
       <c r="P41" s="11">
         <v>2010</v>
       </c>
-      <c r="Q41" s="4"/>
-    </row>
-    <row r="42" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q41" s="11"/>
+      <c r="R41" s="4"/>
+    </row>
+    <row r="42" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A42" s="5" t="s">
         <v>46</v>
       </c>
@@ -2890,9 +2963,10 @@
       <c r="P42" s="11">
         <v>2010</v>
       </c>
-      <c r="Q42" s="2"/>
-    </row>
-    <row r="43" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q42" s="11"/>
+      <c r="R42" s="2"/>
+    </row>
+    <row r="43" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A43" s="5" t="s">
         <v>46</v>
       </c>
@@ -2941,9 +3015,10 @@
       <c r="P43" s="11">
         <v>2010</v>
       </c>
-      <c r="Q43" s="2"/>
-    </row>
-    <row r="44" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q43" s="11"/>
+      <c r="R43" s="2"/>
+    </row>
+    <row r="44" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A44" s="5" t="s">
         <v>46</v>
       </c>
@@ -2992,9 +3067,10 @@
       <c r="P44" s="11">
         <v>2010</v>
       </c>
-      <c r="Q44" s="2"/>
-    </row>
-    <row r="45" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q44" s="11"/>
+      <c r="R44" s="2"/>
+    </row>
+    <row r="45" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A45" s="5" t="s">
         <v>46</v>
       </c>
@@ -3043,9 +3119,10 @@
       <c r="P45" s="11">
         <v>2010</v>
       </c>
-      <c r="Q45" s="4"/>
-    </row>
-    <row r="46" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q45" s="11"/>
+      <c r="R45" s="4"/>
+    </row>
+    <row r="46" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A46" s="5" t="s">
         <v>46</v>
       </c>
@@ -3094,9 +3171,10 @@
       <c r="P46" s="11">
         <v>2010</v>
       </c>
-      <c r="Q46" s="2"/>
-    </row>
-    <row r="47" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q46" s="11"/>
+      <c r="R46" s="2"/>
+    </row>
+    <row r="47" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A47" s="5" t="s">
         <v>80</v>
       </c>
@@ -3141,9 +3219,10 @@
       <c r="P47" s="11">
         <v>2010</v>
       </c>
-      <c r="Q47" s="2"/>
-    </row>
-    <row r="48" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q47" s="11"/>
+      <c r="R47" s="2"/>
+    </row>
+    <row r="48" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A48" s="5" t="s">
         <v>81</v>
       </c>
@@ -3190,9 +3269,10 @@
       <c r="P48" s="11">
         <v>2010</v>
       </c>
-      <c r="Q48" s="2"/>
-    </row>
-    <row r="49" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q48" s="11"/>
+      <c r="R48" s="2"/>
+    </row>
+    <row r="49" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A49" s="5" t="s">
         <v>81</v>
       </c>
@@ -3237,9 +3317,10 @@
       <c r="P49" s="11">
         <v>2010</v>
       </c>
-      <c r="Q49" s="2"/>
-    </row>
-    <row r="50" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q49" s="11"/>
+      <c r="R49" s="2"/>
+    </row>
+    <row r="50" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A50" s="5" t="s">
         <v>81</v>
       </c>
@@ -3288,9 +3369,10 @@
       <c r="P50" s="11">
         <v>2010</v>
       </c>
-      <c r="Q50" s="4"/>
-    </row>
-    <row r="51" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q50" s="11"/>
+      <c r="R50" s="4"/>
+    </row>
+    <row r="51" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A51" s="5" t="s">
         <v>81</v>
       </c>
@@ -3339,9 +3421,10 @@
       <c r="P51" s="11">
         <v>2010</v>
       </c>
-      <c r="Q51" s="2"/>
-    </row>
-    <row r="52" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q51" s="11"/>
+      <c r="R51" s="2"/>
+    </row>
+    <row r="52" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A52" s="5" t="s">
         <v>81</v>
       </c>
@@ -3390,9 +3473,10 @@
       <c r="P52" s="11">
         <v>2010</v>
       </c>
-      <c r="Q52" s="2"/>
-    </row>
-    <row r="53" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q52" s="11"/>
+      <c r="R52" s="2"/>
+    </row>
+    <row r="53" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A53" s="5" t="s">
         <v>81</v>
       </c>
@@ -3441,9 +3525,10 @@
       <c r="P53" s="11">
         <v>2010</v>
       </c>
-      <c r="Q53" s="2"/>
-    </row>
-    <row r="54" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q53" s="11"/>
+      <c r="R53" s="2"/>
+    </row>
+    <row r="54" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A54" s="5" t="s">
         <v>81</v>
       </c>
@@ -3492,9 +3577,10 @@
       <c r="P54" s="11">
         <v>2010</v>
       </c>
-      <c r="Q54" s="4"/>
-    </row>
-    <row r="55" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q54" s="11"/>
+      <c r="R54" s="4"/>
+    </row>
+    <row r="55" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A55" s="5" t="s">
         <v>50</v>
       </c>
@@ -3539,9 +3625,10 @@
       <c r="P55" s="11">
         <v>2010</v>
       </c>
-      <c r="Q55" s="2"/>
-    </row>
-    <row r="56" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q55" s="11"/>
+      <c r="R55" s="2"/>
+    </row>
+    <row r="56" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A56" s="5" t="s">
         <v>86</v>
       </c>
@@ -3586,9 +3673,10 @@
       <c r="P56" s="11">
         <v>2010</v>
       </c>
-      <c r="Q56" s="2"/>
-    </row>
-    <row r="57" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q56" s="11"/>
+      <c r="R56" s="2"/>
+    </row>
+    <row r="57" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A57" s="5" t="s">
         <v>87</v>
       </c>
@@ -3633,9 +3721,10 @@
       <c r="P57" s="11">
         <v>2010</v>
       </c>
-      <c r="Q57" s="2"/>
-    </row>
-    <row r="58" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q57" s="11"/>
+      <c r="R57" s="2"/>
+    </row>
+    <row r="58" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A58" s="5" t="s">
         <v>88</v>
       </c>
@@ -3680,9 +3769,10 @@
       <c r="P58" s="11">
         <v>2010</v>
       </c>
-      <c r="Q58" s="4"/>
-    </row>
-    <row r="59" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q58" s="11"/>
+      <c r="R58" s="4"/>
+    </row>
+    <row r="59" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A59" s="6" t="s">
         <v>89</v>
       </c>
@@ -3727,8 +3817,11 @@
       <c r="P59" s="9">
         <v>2011</v>
       </c>
-    </row>
-    <row r="60" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q59" s="9" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A60" s="6" t="s">
         <v>89</v>
       </c>
@@ -3773,8 +3866,11 @@
       <c r="P60" s="9">
         <v>2011</v>
       </c>
-    </row>
-    <row r="61" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q60" s="9" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A61" s="6" t="s">
         <v>89</v>
       </c>
@@ -3823,8 +3919,11 @@
       <c r="P61" s="9">
         <v>2011</v>
       </c>
-    </row>
-    <row r="62" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q61" s="9" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A62" s="5" t="s">
         <v>89</v>
       </c>
@@ -3873,9 +3972,10 @@
       <c r="P62" s="11">
         <v>2010</v>
       </c>
-      <c r="Q62" s="4"/>
-    </row>
-    <row r="63" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q62" s="11"/>
+      <c r="R62" s="4"/>
+    </row>
+    <row r="63" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A63" s="5" t="s">
         <v>54</v>
       </c>
@@ -3920,8 +4020,9 @@
       <c r="P63" s="11">
         <v>2010</v>
       </c>
-    </row>
-    <row r="64" spans="1:17" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q63" s="11"/>
+    </row>
+    <row r="64" spans="1:18" ht="15" x14ac:dyDescent="0.15">
       <c r="A64" s="5" t="s">
         <v>92</v>
       </c>
@@ -3966,8 +4067,9 @@
       <c r="P64" s="11">
         <v>2010</v>
       </c>
-    </row>
-    <row r="65" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q64" s="11"/>
+    </row>
+    <row r="65" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A65" s="5" t="s">
         <v>93</v>
       </c>
@@ -4012,8 +4114,9 @@
       <c r="P65" s="11">
         <v>2010</v>
       </c>
-    </row>
-    <row r="66" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q65" s="11"/>
+    </row>
+    <row r="66" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A66" s="5" t="s">
         <v>94</v>
       </c>
@@ -4058,8 +4161,9 @@
       <c r="P66" s="11">
         <v>2010</v>
       </c>
-    </row>
-    <row r="67" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q66" s="11"/>
+    </row>
+    <row r="67" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A67" s="5" t="s">
         <v>61</v>
       </c>
@@ -4104,8 +4208,9 @@
       <c r="P67" s="11">
         <v>2010</v>
       </c>
-    </row>
-    <row r="68" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q67" s="11"/>
+    </row>
+    <row r="68" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A68" s="5" t="s">
         <v>95</v>
       </c>
@@ -4150,8 +4255,9 @@
       <c r="P68" s="11">
         <v>2010</v>
       </c>
-    </row>
-    <row r="69" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q68" s="11"/>
+    </row>
+    <row r="69" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A69" s="5" t="s">
         <v>63</v>
       </c>
@@ -4196,8 +4302,9 @@
       <c r="P69" s="11">
         <v>2010</v>
       </c>
-    </row>
-    <row r="70" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q69" s="11"/>
+    </row>
+    <row r="70" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A70" s="5" t="s">
         <v>64</v>
       </c>
@@ -4242,8 +4349,9 @@
       <c r="P70" s="11">
         <v>2010</v>
       </c>
-    </row>
-    <row r="71" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q70" s="11"/>
+    </row>
+    <row r="71" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A71" s="5" t="s">
         <v>68</v>
       </c>
@@ -4288,8 +4396,9 @@
       <c r="P71" s="11">
         <v>2010</v>
       </c>
-    </row>
-    <row r="72" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q71" s="11"/>
+    </row>
+    <row r="72" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A72" s="5" t="s">
         <v>70</v>
       </c>
@@ -4334,8 +4443,9 @@
       <c r="P72" s="11">
         <v>2010</v>
       </c>
-    </row>
-    <row r="73" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q72" s="11"/>
+    </row>
+    <row r="73" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A73" s="5" t="s">
         <v>97</v>
       </c>
@@ -4380,8 +4490,9 @@
       <c r="P73" s="11">
         <v>2010</v>
       </c>
-    </row>
-    <row r="74" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q73" s="11"/>
+    </row>
+    <row r="74" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A74" s="5" t="s">
         <v>71</v>
       </c>
@@ -4426,8 +4537,9 @@
       <c r="P74" s="11">
         <v>2010</v>
       </c>
-    </row>
-    <row r="75" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q74" s="11"/>
+    </row>
+    <row r="75" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A75" s="5" t="s">
         <v>72</v>
       </c>
@@ -4472,8 +4584,9 @@
       <c r="P75" s="11">
         <v>2010</v>
       </c>
-    </row>
-    <row r="76" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q75" s="11"/>
+    </row>
+    <row r="76" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A76" s="5" t="s">
         <v>65</v>
       </c>
@@ -4522,8 +4635,9 @@
       <c r="P76" s="11">
         <v>2009</v>
       </c>
-    </row>
-    <row r="77" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q76" s="11"/>
+    </row>
+    <row r="77" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A77" s="5" t="s">
         <v>98</v>
       </c>
@@ -4572,8 +4686,9 @@
       <c r="P77" s="11">
         <v>2008</v>
       </c>
-    </row>
-    <row r="78" spans="1:16" ht="15" x14ac:dyDescent="0.15">
+      <c r="Q77" s="11"/>
+    </row>
+    <row r="78" spans="1:17" ht="15" x14ac:dyDescent="0.15">
       <c r="A78" s="5" t="s">
         <v>98</v>
       </c>
@@ -4622,6 +4737,7 @@
       <c r="P78" s="11">
         <v>2008</v>
       </c>
+      <c r="Q78" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
